--- a/test_with_images.xlsx
+++ b/test_with_images.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1_8379cccf</t>
+          <t>T1_b4f962ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -545,12 +545,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A_8379cccf</t>
+          <t>A_b4f962ad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>D_8379cccf</t>
+          <t>D_b4f962ad</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -566,7 +566,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T2_d8c62c4d</t>
+          <t>T2_a4759dad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A_d8c62c4d</t>
+          <t>A_a4759dad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D_d8c62c4d</t>
+          <t>D_a4759dad</t>
         </is>
       </c>
       <c r="H3" t="n">

--- a/test_with_images.xlsx
+++ b/test_with_images.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1_b4f962ad</t>
+          <t>T1_daa05a0f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -545,12 +545,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A_b4f962ad</t>
+          <t>A_daa05a0f</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>D_b4f962ad</t>
+          <t>D_daa05a0f</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -566,7 +566,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T2_a4759dad</t>
+          <t>T2_a1cb261e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A_a4759dad</t>
+          <t>A_a1cb261e</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D_a4759dad</t>
+          <t>D_a1cb261e</t>
         </is>
       </c>
       <c r="H3" t="n">
